--- a/output/2026053105021211_東京優駿.xlsx
+++ b/output/2026053105021211_東京優駿.xlsx
@@ -716,10 +716,10 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0862</v>
+        <v>0.0847</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3276</v>
+        <v>0.2881</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -742,11 +742,11 @@
       <c r="P2" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.4074</v>
+      <c r="Q2" t="n">
+        <v>0.2222</v>
       </c>
       <c r="R2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -776,11 +776,11 @@
       <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" s="3" t="n">
-        <v>1</v>
+      <c r="AA2" t="n">
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -830,10 +830,10 @@
         <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0862</v>
+        <v>0.0847</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3276</v>
+        <v>0.2881</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2</v>
+        <v>0.1429</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -890,11 +890,11 @@
       <c r="Z3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA3" s="3" t="n">
-        <v>0.3016</v>
+      <c r="AA3" t="n">
+        <v>0.254</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AC3" s="3" t="n">
         <v>2</v>
@@ -947,10 +947,10 @@
         <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0517</v>
+        <v>0.0508</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3448</v>
+        <v>0.3051</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2857</v>
+        <v>0.2381</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2593</v>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>7</v>
+        <v>0.1481</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4</v>
       </c>
       <c r="AC4" t="n">
         <v>4</v>
@@ -1064,10 +1064,10 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0517</v>
+        <v>0.0508</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3448</v>
+        <v>0.3051</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1090,11 +1090,11 @@
       <c r="P5" t="n">
         <v>5</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.3385</v>
+      <c r="Q5" t="n">
+        <v>0.2769</v>
       </c>
       <c r="R5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1125,10 +1125,10 @@
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>2</v>
@@ -1181,10 +1181,10 @@
         <v>4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.1552</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.3793</v>
+        <v>0.1525</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.339</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1208,10 +1208,10 @@
         <v>4</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.4839</v>
+        <v>0.3871</v>
       </c>
       <c r="R6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         <v>6</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.2338</v>
+        <v>0.2208</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1241,11 +1241,11 @@
       <c r="Z6" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AA6" s="3" t="n">
-        <v>0.35</v>
+      <c r="AA6" t="n">
+        <v>0.25</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AC6" t="n">
         <v>14</v>
@@ -1298,10 +1298,10 @@
         <v>3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1552</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.3793</v>
+        <v>0.1525</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.339</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1324,11 +1324,11 @@
       <c r="P7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.4545</v>
+      <c r="Q7" t="n">
+        <v>0.2727</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1342,10 +1342,10 @@
         <v>6</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>0.2338</v>
+        <v>0.2208</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1358,11 +1358,11 @@
       <c r="Z7" t="n">
         <v>2</v>
       </c>
-      <c r="AA7" s="3" t="n">
-        <v>0.5833</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>7</v>
+      <c r="AA7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3</v>
       </c>
       <c r="AC7" s="3" t="n">
         <v>1</v>
@@ -1415,10 +1415,10 @@
         <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0517</v>
+        <v>0.0508</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3103</v>
+        <v>0.2712</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2727</v>
+        <v>0.1818</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="3" t="n">
         <v>1</v>
@@ -1532,10 +1532,10 @@
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0517</v>
+        <v>0.0508</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3103</v>
+        <v>0.2712</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2222</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         <v>6</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>0.2338</v>
+        <v>0.2208</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
         <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.2836</v>
+        <v>0.2388</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1034</v>
+        <v>0.1017</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3103</v>
+        <v>0.2542</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         <v>8</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>30</v>
+        <v>0.4906</v>
+      </c>
+      <c r="R10" t="n">
+        <v>26</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
         <v>6</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>0.2338</v>
+        <v>0.2208</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1707,10 +1707,10 @@
         <v>6</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>0.3727</v>
+        <v>0.3091</v>
       </c>
       <c r="AB10" s="3" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="AC10" s="3" t="n">
         <v>1</v>
@@ -1763,10 +1763,10 @@
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1034</v>
+        <v>0.1017</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3103</v>
+        <v>0.2542</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1789,11 +1789,11 @@
       <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" s="3" t="n">
-        <v>0.36</v>
+      <c r="Q11" t="n">
+        <v>0.28</v>
       </c>
       <c r="R11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1823,11 +1823,11 @@
       <c r="Z11" t="n">
         <v>1</v>
       </c>
-      <c r="AA11" s="3" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>9</v>
+      <c r="AA11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4</v>
       </c>
       <c r="AC11" t="n">
         <v>4</v>
@@ -1880,10 +1880,10 @@
         <v>5</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.1724</v>
+        <v>0.1695</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4576</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -1906,11 +1906,11 @@
       <c r="P12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" s="3" t="n">
-        <v>0.3</v>
+      <c r="Q12" t="n">
+        <v>0.2333</v>
       </c>
       <c r="R12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       <c r="Z12" t="n">
         <v>0</v>
       </c>
-      <c r="AA12" s="3" t="n">
-        <v>0.5</v>
+      <c r="AA12" t="n">
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -1994,10 +1994,10 @@
         <v>8</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.1724</v>
+        <v>0.1695</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4576</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -2021,27 +2021,27 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>三嶋牧場</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="R13" t="n">
-        <v>5</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>三嶋牧場</t>
-        </is>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="W13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2054,11 +2054,11 @@
       <c r="Z13" t="n">
         <v>0</v>
       </c>
-      <c r="AA13" s="3" t="n">
-        <v>0.3</v>
+      <c r="AA13" t="n">
+        <v>0.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
         <v>5</v>
@@ -2111,10 +2111,10 @@
         <v>4</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.1897</v>
+        <v>0.1864</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4407</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2138,10 +2138,10 @@
         <v>36</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.7526</v>
+        <v>0.6907</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         <v>6</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>0.3727</v>
+        <v>0.3091</v>
       </c>
       <c r="AB14" s="3" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="AC14" s="3" t="n">
         <v>1</v>
@@ -2228,10 +2228,10 @@
         <v>6</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.1897</v>
+        <v>0.1864</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4407</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         <v>4</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>0.3704</v>
+        <v>0.3333</v>
       </c>
       <c r="R15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2288,11 +2288,11 @@
       <c r="Z15" t="n">
         <v>2</v>
       </c>
-      <c r="AA15" s="3" t="n">
-        <v>0.5833</v>
-      </c>
-      <c r="AB15" s="3" t="n">
-        <v>7</v>
+      <c r="AA15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3</v>
       </c>
       <c r="AC15" s="3" t="n">
         <v>1</v>
@@ -2345,10 +2345,10 @@
         <v>4</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.1897</v>
+        <v>0.1864</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4407</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -2372,10 +2372,10 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2353</v>
+        <v>0.0588</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2389,10 +2389,10 @@
         <v>6</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0.2338</v>
+        <v>0.2208</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2406,10 +2406,10 @@
         <v>3</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3889</v>
       </c>
       <c r="AB16" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2459,10 +2459,10 @@
         <v>4</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.1724</v>
+        <v>0.1695</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.6034</v>
+        <v>0.4915</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2486,10 +2486,10 @@
         <v>8</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>0.3977</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>35</v>
+        <v>0.3295</v>
+      </c>
+      <c r="R17" t="n">
+        <v>29</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2519,11 +2519,11 @@
       <c r="Z17" t="n">
         <v>2</v>
       </c>
-      <c r="AA17" s="3" t="n">
-        <v>0.3158</v>
-      </c>
-      <c r="AB17" s="3" t="n">
-        <v>6</v>
+      <c r="AA17" t="n">
+        <v>0.2105</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4</v>
       </c>
       <c r="AC17" s="3" t="n">
         <v>2</v>
@@ -2576,10 +2576,10 @@
         <v>4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.1724</v>
+        <v>0.1695</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.6034</v>
+        <v>0.4915</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2603,10 +2603,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2727</v>
+        <v>0.1818</v>
       </c>
       <c r="R18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
         <v>6</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>0.2338</v>
+        <v>0.2208</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2636,11 +2636,11 @@
       <c r="Z18" t="n">
         <v>0</v>
       </c>
-      <c r="AA18" s="3" t="n">
-        <v>1</v>
+      <c r="AA18" t="n">
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2690,10 +2690,10 @@
         <v>6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.1724</v>
+        <v>0.1695</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.6034</v>
+        <v>0.4915</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2716,11 +2716,11 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="3" t="n">
-        <v>0.6667</v>
+      <c r="Q19" t="n">
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2734,10 +2734,10 @@
         <v>6</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>0.2338</v>
+        <v>0.2208</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2750,11 +2750,11 @@
       <c r="Z19" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AA19" s="3" t="n">
-        <v>0.35</v>
+      <c r="AA19" t="n">
+        <v>0.25</v>
       </c>
       <c r="AB19" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AC19" t="n">
         <v>14</v>
